--- a/data/reports/PHASE_2_VALIDATION_REPORT.xlsx
+++ b/data/reports/PHASE_2_VALIDATION_REPORT.xlsx
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1754</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="3">
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -596,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C439"/>
+  <dimension ref="A1:C437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -679,7 +679,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -694,7 +694,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -709,7 +709,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -754,7 +754,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -769,7 +769,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -784,7 +784,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -814,7 +814,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -829,7 +829,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -889,7 +889,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -904,7 +904,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,7 +919,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -934,7 +934,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -949,7 +949,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -979,7 +979,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -994,7 +994,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1009,7 +1009,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1024,7 +1024,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1054,7 +1054,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1069,7 +1069,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1084,7 +1084,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1099,7 +1099,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1114,7 +1114,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1129,7 +1129,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1144,7 +1144,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1174,7 +1174,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1189,7 +1189,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1204,7 +1204,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1219,7 +1219,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1234,7 +1234,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1249,7 +1249,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1264,7 +1264,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1294,7 +1294,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1324,7 +1324,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1354,7 +1354,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1384,7 +1384,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1399,7 +1399,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1414,7 +1414,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1459,7 +1459,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1474,7 +1474,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1489,7 +1489,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1504,7 +1504,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1549,7 +1549,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1564,7 +1564,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1579,7 +1579,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1594,7 +1594,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1609,7 +1609,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1624,7 +1624,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1639,7 +1639,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1654,7 +1654,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1669,7 +1669,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1684,7 +1684,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1699,7 +1699,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1714,7 +1714,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1729,7 +1729,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1744,7 +1744,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1774,7 +1774,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1789,7 +1789,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1804,7 +1804,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1819,7 +1819,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1834,7 +1834,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1849,7 +1849,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1864,7 +1864,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1879,7 +1879,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1894,7 +1894,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1909,7 +1909,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1924,7 +1924,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1939,7 +1939,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1954,7 +1954,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1969,7 +1969,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1984,7 +1984,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1999,7 +1999,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2014,7 +2014,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2029,7 +2029,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2044,7 +2044,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2059,7 +2059,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2074,7 +2074,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2104,7 +2104,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2119,7 +2119,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2164,7 +2164,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2179,7 +2179,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2194,7 +2194,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2209,7 +2209,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2224,7 +2224,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2239,7 +2239,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2254,7 +2254,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2269,7 +2269,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2284,7 +2284,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2299,7 +2299,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2314,7 +2314,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2329,7 +2329,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2344,7 +2344,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2359,7 +2359,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2374,7 +2374,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2389,7 +2389,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2404,7 +2404,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2434,7 +2434,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2449,7 +2449,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2464,7 +2464,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2479,7 +2479,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2494,7 +2494,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2509,7 +2509,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2524,7 +2524,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2554,7 +2554,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2569,7 +2569,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2584,7 +2584,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2599,7 +2599,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2614,7 +2614,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -2629,7 +2629,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2644,7 +2644,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2659,7 +2659,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2674,7 +2674,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2689,7 +2689,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2704,7 +2704,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2719,7 +2719,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2749,7 +2749,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2764,7 +2764,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2779,7 +2779,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2794,7 +2794,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -2809,7 +2809,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -2824,7 +2824,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -2854,7 +2854,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -2869,7 +2869,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2884,7 +2884,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -2899,7 +2899,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -2914,7 +2914,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -2929,7 +2929,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -2944,7 +2944,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -2959,7 +2959,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -2974,7 +2974,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -2989,7 +2989,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3004,7 +3004,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3019,7 +3019,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3034,7 +3034,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3049,7 +3049,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3064,7 +3064,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3094,7 +3094,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3109,7 +3109,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3124,7 +3124,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3139,7 +3139,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -3154,7 +3154,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3169,7 +3169,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3184,7 +3184,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3199,7 +3199,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3214,7 +3214,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -3229,7 +3229,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3244,7 +3244,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -3259,7 +3259,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3274,7 +3274,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -3289,7 +3289,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -3304,7 +3304,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -3319,7 +3319,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -3334,7 +3334,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -3349,7 +3349,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -3364,7 +3364,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -3394,7 +3394,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -3409,7 +3409,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -3424,7 +3424,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -3439,7 +3439,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -3454,7 +3454,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -3469,7 +3469,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -3484,7 +3484,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -3499,7 +3499,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -3514,7 +3514,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -3529,7 +3529,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -3544,7 +3544,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -3559,7 +3559,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -3589,7 +3589,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -3604,7 +3604,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -3619,7 +3619,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -3634,7 +3634,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -3649,7 +3649,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -3664,7 +3664,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -3679,7 +3679,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -3694,7 +3694,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -3709,7 +3709,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -3724,7 +3724,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -3739,7 +3739,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -3754,7 +3754,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -3769,7 +3769,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -3784,7 +3784,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -3799,7 +3799,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -3814,7 +3814,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -3829,7 +3829,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -3844,7 +3844,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -3859,7 +3859,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -3874,7 +3874,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -3889,7 +3889,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -3904,7 +3904,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -3919,7 +3919,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -3934,7 +3934,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -3949,7 +3949,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -3964,7 +3964,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -3979,7 +3979,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -3994,7 +3994,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -4009,7 +4009,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -4039,7 +4039,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -4069,7 +4069,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -4084,7 +4084,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -4099,7 +4099,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -4114,7 +4114,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -4129,7 +4129,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -4144,7 +4144,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -4159,7 +4159,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -4174,7 +4174,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -4189,7 +4189,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -4204,7 +4204,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -4219,7 +4219,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -4234,7 +4234,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -4264,7 +4264,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -4279,7 +4279,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -4294,7 +4294,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -4309,7 +4309,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -4324,7 +4324,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -4339,7 +4339,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -4354,7 +4354,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -4369,7 +4369,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -4384,7 +4384,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -4399,7 +4399,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -4414,7 +4414,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -4429,7 +4429,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -4444,7 +4444,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -4459,7 +4459,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -4474,7 +4474,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -4489,7 +4489,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -4504,7 +4504,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -4519,7 +4519,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -4534,7 +4534,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -4549,7 +4549,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -4564,7 +4564,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -4579,7 +4579,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -4594,7 +4594,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -4609,7 +4609,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -4624,7 +4624,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -4639,7 +4639,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -4654,7 +4654,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -4684,7 +4684,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -4699,7 +4699,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -4714,7 +4714,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -4729,7 +4729,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -4744,7 +4744,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -4759,7 +4759,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -4774,7 +4774,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -4789,7 +4789,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -4804,7 +4804,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -4819,7 +4819,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -4834,7 +4834,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -4849,7 +4849,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -4864,7 +4864,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -4879,7 +4879,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -4894,7 +4894,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -4909,7 +4909,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -4924,7 +4924,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -4939,7 +4939,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -4954,7 +4954,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -4969,7 +4969,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -4984,7 +4984,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -4999,7 +4999,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -5014,7 +5014,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -5029,7 +5029,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -5044,7 +5044,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -5059,7 +5059,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -5074,7 +5074,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -5089,7 +5089,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -5104,7 +5104,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -5119,7 +5119,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -5134,7 +5134,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -5149,7 +5149,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -5164,7 +5164,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -5179,7 +5179,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -5194,7 +5194,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -5209,7 +5209,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -5224,7 +5224,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -5239,7 +5239,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -5254,7 +5254,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -5269,7 +5269,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -5284,7 +5284,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -5299,7 +5299,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -5314,7 +5314,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -5329,7 +5329,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -5344,7 +5344,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -5359,7 +5359,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -5374,7 +5374,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -5389,7 +5389,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -5404,7 +5404,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -5419,7 +5419,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -5434,7 +5434,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -5449,7 +5449,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -5464,7 +5464,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -5479,7 +5479,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -5494,7 +5494,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -5509,7 +5509,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -5524,7 +5524,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -5539,7 +5539,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -5554,7 +5554,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -5569,7 +5569,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -5584,7 +5584,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -5599,7 +5599,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -5614,7 +5614,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -5629,7 +5629,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -5644,7 +5644,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -5659,7 +5659,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -5674,7 +5674,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -5689,7 +5689,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -5704,7 +5704,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -5719,7 +5719,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -5734,7 +5734,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -5749,7 +5749,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -5764,7 +5764,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -5779,7 +5779,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -5794,7 +5794,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -5809,7 +5809,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -5824,7 +5824,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -5839,7 +5839,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -5854,7 +5854,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -5869,7 +5869,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -5884,7 +5884,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -5899,7 +5899,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -5914,7 +5914,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -5929,7 +5929,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -5944,7 +5944,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -5974,7 +5974,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -5989,7 +5989,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -6004,7 +6004,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -6019,7 +6019,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -6034,7 +6034,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -6049,7 +6049,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -6064,7 +6064,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -6079,7 +6079,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -6094,7 +6094,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -6109,7 +6109,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -6124,7 +6124,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -6139,7 +6139,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -6154,7 +6154,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -6169,7 +6169,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -6184,7 +6184,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -6199,7 +6199,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -6214,7 +6214,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -6229,7 +6229,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -6244,7 +6244,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -6259,7 +6259,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -6274,7 +6274,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -6289,7 +6289,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -6304,7 +6304,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -6319,7 +6319,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -6334,7 +6334,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -6349,7 +6349,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -6364,7 +6364,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -6379,7 +6379,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -6394,7 +6394,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -6409,7 +6409,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -6424,7 +6424,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -6439,7 +6439,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -6454,7 +6454,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -6469,7 +6469,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -6484,7 +6484,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -6499,7 +6499,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -6514,7 +6514,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -6529,7 +6529,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -6544,7 +6544,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -6559,7 +6559,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -6574,7 +6574,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -6589,7 +6589,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -6619,7 +6619,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -6634,7 +6634,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -6649,7 +6649,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -6664,7 +6664,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -6679,7 +6679,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -6694,7 +6694,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -6709,7 +6709,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -6724,7 +6724,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -6739,7 +6739,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -6754,7 +6754,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -6769,7 +6769,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -6784,7 +6784,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -6799,7 +6799,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -6814,7 +6814,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -6829,7 +6829,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -6844,7 +6844,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -6859,7 +6859,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -6874,7 +6874,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -6889,7 +6889,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -6904,7 +6904,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -6919,7 +6919,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -6934,7 +6934,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -6949,7 +6949,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -6964,7 +6964,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -6979,7 +6979,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -6994,7 +6994,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -7009,7 +7009,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -7024,7 +7024,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -7039,7 +7039,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -7054,7 +7054,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -7069,7 +7069,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -7084,7 +7084,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -7099,7 +7099,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -7114,7 +7114,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -7129,7 +7129,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -7144,7 +7144,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -7153,36 +7153,6 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>Midday</t>
-        </is>
-      </c>
-      <c r="C438" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>Evening</t>
-        </is>
-      </c>
-      <c r="C439" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7253,7 +7223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1755"/>
+  <dimension ref="A1:H1757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70442,6 +70412,78 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="1756">
+      <c r="A1756" t="n">
+        <v>1755</v>
+      </c>
+      <c r="B1756" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>Midday</t>
+        </is>
+      </c>
+      <c r="D1756" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="E1756" t="inlineStr">
+        <is>
+          <t>047</t>
+        </is>
+      </c>
+      <c r="F1756" t="inlineStr">
+        <is>
+          <t>https://www.lottery.net/new-jersey/pick-3-midday/results/2026</t>
+        </is>
+      </c>
+      <c r="G1756" t="inlineStr">
+        <is>
+          <t>2026-05-30 05:56:22</t>
+        </is>
+      </c>
+      <c r="H1756" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="n">
+        <v>1756</v>
+      </c>
+      <c r="B1757" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="D1757" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="E1757" t="inlineStr">
+        <is>
+          <t>049</t>
+        </is>
+      </c>
+      <c r="F1757" t="inlineStr">
+        <is>
+          <t>https://www.lottery.net/new-jersey/pick-3-evening/results/2026</t>
+        </is>
+      </c>
+      <c r="G1757" t="inlineStr">
+        <is>
+          <t>2026-05-30 05:56:22</t>
+        </is>
+      </c>
+      <c r="H1757" t="n">
+        <v>2026</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
